--- a/data/trans_orig/P37C1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023</t>
+          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2417</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1668</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10052</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2417</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10854</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>11605</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2417</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9827</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>38354</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23888</t>
+          <t>24335</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56462</t>
+          <t>55056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106605</t>
+          <t>108915</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145670</t>
+          <t>148968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114081</t>
+          <t>113444</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144598</t>
+          <t>142428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231481</t>
+          <t>231494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>283280</t>
+          <t>281828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449558</t>
+          <t>447037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492992</t>
+          <t>493048</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>503547</t>
+          <t>505877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>537251</t>
+          <t>537871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>964592</t>
+          <t>962855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019965</t>
+          <t>1018789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>22198</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61357</t>
+          <t>59045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>82499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104846</t>
+          <t>117081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>287053</t>
+          <t>280919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>192327</t>
+          <t>192838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>235428</t>
+          <t>233604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284962</t>
+          <t>264369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>500599</t>
+          <t>499658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830904</t>
+          <t>836504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1050378</t>
+          <t>1033157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689092</t>
+          <t>690718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733740</t>
+          <t>733696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1547290</t>
+          <t>1543941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1799897</t>
+          <t>1828546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>313</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>11271</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40161</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35978</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29281</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66249</t>
+          <t>66147</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>180222</t>
+          <t>180283</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237944</t>
+          <t>241875</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73985</t>
+          <t>75166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198640</t>
+          <t>198939</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>214050</t>
+          <t>219053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>419834</t>
+          <t>420848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>426964</t>
+          <t>427202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>486392</t>
+          <t>488189</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>699564</t>
+          <t>699608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>844045</t>
+          <t>840088</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1142605</t>
+          <t>1141921</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1376909</t>
+          <t>1373590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29729</t>
+          <t>29177</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55748</t>
+          <t>54712</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24221</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47335</t>
+          <t>46663</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>58872</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93783</t>
+          <t>95214</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>124734</t>
+          <t>122526</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>173694</t>
+          <t>170763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141015</t>
+          <t>142427</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203640</t>
+          <t>203630</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>285072</t>
+          <t>278512</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>360621</t>
+          <t>359744</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>693344</t>
+          <t>697085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>746204</t>
+          <t>750105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>838494</t>
+          <t>839005</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>910743</t>
+          <t>910460</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1548028</t>
+          <t>1549301</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1640980</t>
+          <t>1644539</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>37280</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>37094</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25680</t>
+          <t>24609</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104141</t>
+          <t>102506</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>163464</t>
+          <t>162526</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>73394</t>
+          <t>73397</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>114404</t>
+          <t>115476</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>190048</t>
+          <t>189601</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>260180</t>
+          <t>262299</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>569776</t>
+          <t>550491</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>768826</t>
+          <t>771707</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>533214</t>
+          <t>540784</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>722385</t>
+          <t>729519</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1180851</t>
+          <t>1176479</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1467430</t>
+          <t>1470616</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2481958</t>
+          <t>2474193</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2732579</t>
+          <t>2750697</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2792575</t>
+          <t>2786360</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3003513</t>
+          <t>3005311</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5306822</t>
+          <t>5298955</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5646835</t>
+          <t>5645567</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Habitat-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>13096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24738</t>
+          <t>34254</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>23371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>51228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24335</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>41595</t>
+          <t>55294</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30892</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55056</t>
+          <t>74185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>126609</t>
+          <t>139911</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108915</t>
+          <t>118052</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148968</t>
+          <t>162504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>127842</t>
+          <t>138550</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113444</t>
+          <t>121893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142428</t>
+          <t>155336</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>254451</t>
+          <t>278461</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231494</t>
+          <t>252185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>281828</t>
+          <t>305770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>471165</t>
+          <t>501395</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447037</t>
+          <t>476271</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493048</t>
+          <t>524169</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>521530</t>
+          <t>563609</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>505877</t>
+          <t>544363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>537871</t>
+          <t>579919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>992695</t>
+          <t>1065003</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>962855</t>
+          <t>1036255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1018789</t>
+          <t>1094651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>627920</t>
+          <t>681883</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>627920</t>
+          <t>681883</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>627920</t>
+          <t>681883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>670768</t>
+          <t>727702</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>670768</t>
+          <t>727702</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>670768</t>
+          <t>727702</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1298688</t>
+          <t>1409584</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1298688</t>
+          <t>1409584</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1298688</t>
+          <t>1409584</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>12486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>14402</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>15704</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22198</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41127</t>
+          <t>48043</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>36101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59045</t>
+          <t>65813</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>61653</t>
+          <t>71764</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>56660</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82499</t>
+          <t>89775</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>217543</t>
+          <t>247273</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117081</t>
+          <t>218465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280919</t>
+          <t>280447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>211785</t>
+          <t>235704</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>192838</t>
+          <t>210772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>233604</t>
+          <t>259876</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>429328</t>
+          <t>482977</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264369</t>
+          <t>445177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>499658</t>
+          <t>524553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>915388</t>
+          <t>732384</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836504</t>
+          <t>699428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1033157</t>
+          <t>765404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>712844</t>
+          <t>797314</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>690718</t>
+          <t>772964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733696</t>
+          <t>821732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1628231</t>
+          <t>1529698</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1543941</t>
+          <t>1486087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1828546</t>
+          <t>1570986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1186487</t>
+          <t>1040096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1186487</t>
+          <t>1040096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1186487</t>
+          <t>1040096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>955633</t>
+          <t>1068203</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>955633</t>
+          <t>1068203</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>955633</t>
+          <t>1068203</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2142120</t>
+          <t>2108299</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2142120</t>
+          <t>2108299</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2142120</t>
+          <t>2108299</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>18348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26458</t>
+          <t>35078</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>23664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38864</t>
+          <t>49854</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>46639</t>
+          <t>57894</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29148</t>
+          <t>42689</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>80279</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>205396</t>
+          <t>230913</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>180283</t>
+          <t>201029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>241875</t>
+          <t>261397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>147239</t>
+          <t>175363</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75166</t>
+          <t>155380</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198939</t>
+          <t>197517</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>352636</t>
+          <t>406276</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>219053</t>
+          <t>372278</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>420848</t>
+          <t>446667</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>459249</t>
+          <t>515705</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>427202</t>
+          <t>482757</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>488189</t>
+          <t>548165</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>759238</t>
+          <t>606000</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>699608</t>
+          <t>582357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>840088</t>
+          <t>629038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1218488</t>
+          <t>1121705</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1141921</t>
+          <t>1084450</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1373590</t>
+          <t>1160973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>701643</t>
+          <t>794461</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>701643</t>
+          <t>794461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>701643</t>
+          <t>794461</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>930933</t>
+          <t>809674</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>930933</t>
+          <t>809674</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>930933</t>
+          <t>809674</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1632576</t>
+          <t>1604135</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1632576</t>
+          <t>1604135</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1632576</t>
+          <t>1604135</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,17 +2806,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>24223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41554</t>
+          <t>48966</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29177</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54712</t>
+          <t>66508</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>34468</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46663</t>
+          <t>52531</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>76022</t>
+          <t>87991</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58872</t>
+          <t>70610</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95214</t>
+          <t>109191</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>146490</t>
+          <t>162220</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>122526</t>
+          <t>139013</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>170763</t>
+          <t>189044</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>177118</t>
+          <t>191847</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>142427</t>
+          <t>169152</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203630</t>
+          <t>215617</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>323608</t>
+          <t>354067</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>278512</t>
+          <t>320549</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>359744</t>
+          <t>391340</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>720401</t>
+          <t>760432</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>697085</t>
+          <t>729118</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>750105</t>
+          <t>786304</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>868174</t>
+          <t>876455</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>839005</t>
+          <t>849845</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>910460</t>
+          <t>899034</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1588576</t>
+          <t>1636887</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1549301</t>
+          <t>1600546</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1644539</t>
+          <t>1674731</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>918527</t>
+          <t>982225</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>918527</t>
+          <t>982225</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>918527</t>
+          <t>982225</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1087635</t>
+          <t>1115271</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1087635</t>
+          <t>1115271</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1087635</t>
+          <t>1115271</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2006163</t>
+          <t>2097496</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2006163</t>
+          <t>2097496</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2006163</t>
+          <t>2097496</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>43666</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>47884</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>56548</t>
+          <t>65639</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>133877</t>
+          <t>166341</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>102506</t>
+          <t>141103</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>162526</t>
+          <t>201062</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>92033</t>
+          <t>106602</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>73397</t>
+          <t>89719</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>115476</t>
+          <t>128026</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>225909</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>189601</t>
+          <t>237894</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>262299</t>
+          <t>307347</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>696038</t>
+          <t>780317</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>550491</t>
+          <t>724238</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>771707</t>
+          <t>836341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>663984</t>
+          <t>741464</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>540784</t>
+          <t>698674</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>729519</t>
+          <t>783147</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1360022</t>
+          <t>1521781</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1176479</t>
+          <t>1453889</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1470616</t>
+          <t>1590458</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2566204</t>
+          <t>2509916</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2474193</t>
+          <t>2449736</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2750697</t>
+          <t>2571303</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2861786</t>
+          <t>2843378</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2786360</t>
+          <t>2799457</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3005311</t>
+          <t>2889756</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5427989</t>
+          <t>5353294</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5298955</t>
+          <t>5281697</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5645567</t>
+          <t>5424714</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3434578</t>
+          <t>3498664</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3434578</t>
+          <t>3498664</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3434578</t>
+          <t>3498664</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3644969</t>
+          <t>3720850</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3644969</t>
+          <t>3720850</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3644969</t>
+          <t>3720850</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7079546</t>
+          <t>7219514</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7079546</t>
+          <t>7219514</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7079546</t>
+          <t>7219514</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
